--- a/xlsx/Power/p18.xlsx
+++ b/xlsx/Power/p18.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD9071F-AE37-4811-9D31-262680F3C870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFE5434-C993-4B73-A1AC-B57FE421245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1A7043A5-AF46-403E-B576-2043D8964B41}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1A7043A5-AF46-403E-B576-2043D8964B41}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,13 +404,13 @@
         <v>0.74199999999999999</v>
       </c>
       <c r="C1">
-        <v>0.93100000000000005</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="D1">
-        <v>0.99399999999999999</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="E1">
-        <v>0.999</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="F1">
         <v>1</v>
@@ -436,19 +436,19 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="C2">
-        <v>0.77800000000000002</v>
+        <v>1.9E-2</v>
       </c>
       <c r="D2">
-        <v>0.95199999999999996</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="E2">
-        <v>0.997</v>
+        <v>0.83899999999999997</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0.97899999999999998</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -468,13 +468,13 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="C3">
-        <v>0.84199999999999997</v>
+        <v>0.876</v>
       </c>
       <c r="D3">
-        <v>0.96199999999999997</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="E3">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -494,22 +494,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.251</v>
+        <v>0.28499999999999998</v>
       </c>
       <c r="B4">
-        <v>0.48799999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="C4">
-        <v>0.71699999999999997</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="D4">
-        <v>0.88800000000000001</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="E4">
-        <v>0.95199999999999996</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="F4">
-        <v>0.98499999999999999</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="G4">
         <v>0.995</v>
@@ -564,25 +564,25 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="C6">
-        <v>4.0000000000000001E-3</v>
+        <v>0.749</v>
       </c>
       <c r="D6">
-        <v>0.08</v>
+        <v>0.53900000000000003</v>
       </c>
       <c r="E6">
-        <v>0.39100000000000001</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="F6">
-        <v>0.79800000000000004</v>
+        <v>0.89</v>
       </c>
       <c r="G6">
-        <v>0.95599999999999996</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="H6">
-        <v>0.997</v>
+        <v>0.998</v>
       </c>
       <c r="I6">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -596,13 +596,13 @@
         <v>0.49399999999999999</v>
       </c>
       <c r="C7">
-        <v>0.82199999999999995</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="D7">
-        <v>0.96299999999999997</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="E7">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
       <c r="F7">
         <v>0.997</v>
@@ -628,13 +628,13 @@
         <v>0.92600000000000005</v>
       </c>
       <c r="C8">
-        <v>0.98799999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="D8">
+        <v>0.97099999999999997</v>
+      </c>
+      <c r="E8">
         <v>0.999</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>5.5E-2</v>
       </c>
       <c r="C9">
-        <v>7.0000000000000001E-3</v>
+        <v>7.8E-2</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="E9">
-        <v>0.157</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="F9">
-        <v>0.69799999999999995</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="G9">
-        <v>0.88300000000000001</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="H9">
-        <v>0.97</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="I9">
-        <v>0.98</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="J9">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p18.xlsx
+++ b/xlsx/Power/p18.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFE5434-C993-4B73-A1AC-B57FE421245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4249F33-9CD4-4315-ADE3-680FBBD069EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1A7043A5-AF46-403E-B576-2043D8964B41}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1A7043A5-AF46-403E-B576-2043D8964B41}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="B1">
         <v>0.74199999999999999</v>
       </c>
       <c r="C1">
-        <v>0.10199999999999999</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="D1">
-        <v>0.72599999999999998</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="E1">
-        <v>0.96499999999999997</v>
+        <v>0.999</v>
       </c>
       <c r="F1">
         <v>1</v>
@@ -436,19 +436,19 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="C2">
-        <v>1.9E-2</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="D2">
-        <v>0.45500000000000002</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="E2">
-        <v>0.83899999999999997</v>
+        <v>0.997</v>
       </c>
       <c r="F2">
-        <v>0.97899999999999998</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -468,13 +468,13 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="C3">
-        <v>0.876</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="D3">
-        <v>0.96399999999999997</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="E3">
-        <v>0.996</v>
+        <v>0.995</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -494,22 +494,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.28499999999999998</v>
+        <v>0.251</v>
       </c>
       <c r="B4">
-        <v>0.52</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="C4">
-        <v>0.72799999999999998</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="D4">
-        <v>0.88400000000000001</v>
+        <v>0.88700000000000001</v>
       </c>
       <c r="E4">
-        <v>0.95299999999999996</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="F4">
-        <v>0.98599999999999999</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="G4">
         <v>0.995</v>
@@ -564,25 +564,25 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="C6">
-        <v>0.749</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D6">
-        <v>0.53900000000000003</v>
+        <v>0.08</v>
       </c>
       <c r="E6">
-        <v>0.70499999999999996</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="F6">
-        <v>0.89</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="G6">
-        <v>0.96499999999999997</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="H6">
+        <v>0.997</v>
+      </c>
+      <c r="I6">
         <v>0.998</v>
-      </c>
-      <c r="I6">
-        <v>0.999</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -596,13 +596,13 @@
         <v>0.49399999999999999</v>
       </c>
       <c r="C7">
-        <v>0.81499999999999995</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="D7">
-        <v>0.96199999999999997</v>
+        <v>0.96299999999999997</v>
       </c>
       <c r="E7">
-        <v>0.996</v>
+        <v>0.995</v>
       </c>
       <c r="F7">
         <v>0.997</v>
@@ -628,13 +628,13 @@
         <v>0.92600000000000005</v>
       </c>
       <c r="C8">
-        <v>0.21</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="D8">
-        <v>0.97099999999999997</v>
+        <v>0.999</v>
       </c>
       <c r="E8">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>5.5E-2</v>
       </c>
       <c r="C9">
-        <v>7.8E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D9">
-        <v>8.2000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.81100000000000005</v>
+        <v>0.157</v>
       </c>
       <c r="F9">
-        <v>0.85699999999999998</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="G9">
-        <v>0.92700000000000005</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="H9">
-        <v>0.98499999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="I9">
-        <v>0.98399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="J9">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p18.xlsx
+++ b/xlsx/Power/p18.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4249F33-9CD4-4315-ADE3-680FBBD069EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AFA647-89D1-4DEF-B1EB-30B22A6764C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1A7043A5-AF46-403E-B576-2043D8964B41}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{1A7043A5-AF46-403E-B576-2043D8964B41}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,13 +398,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.318</v>
+        <v>0.315</v>
       </c>
       <c r="B1">
-        <v>0.74199999999999999</v>
+        <v>0.748</v>
       </c>
       <c r="C1">
-        <v>0.93100000000000005</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="D1">
         <v>0.99399999999999999</v>
@@ -430,13 +430,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.19700000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="B2">
-        <v>0.46600000000000003</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="C2">
-        <v>0.77800000000000002</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="D2">
         <v>0.95199999999999996</v>
@@ -462,13 +462,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.28299999999999997</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="B3">
-        <v>0.61499999999999999</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="C3">
-        <v>0.84199999999999997</v>
+        <v>0.85</v>
       </c>
       <c r="D3">
         <v>0.96199999999999997</v>
@@ -494,22 +494,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.251</v>
+        <v>0.246</v>
       </c>
       <c r="B4">
-        <v>0.48799999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="C4">
-        <v>0.71699999999999997</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="D4">
-        <v>0.88700000000000001</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="E4">
-        <v>0.95199999999999996</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="F4">
-        <v>0.98499999999999999</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="G4">
         <v>0.995</v>
@@ -526,39 +526,39 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.184</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.40100000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>3.1E-2</v>
+        <v>0.03</v>
       </c>
       <c r="B6">
         <v>7.0000000000000001E-3</v>
@@ -567,19 +567,19 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D6">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E6">
-        <v>0.39100000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="F6">
-        <v>0.79800000000000004</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="G6">
-        <v>0.95599999999999996</v>
+        <v>0.94299999999999995</v>
       </c>
       <c r="H6">
-        <v>0.997</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="I6">
         <v>0.998</v>
@@ -590,16 +590,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5.7000000000000002E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="B7">
-        <v>0.49399999999999999</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="C7">
         <v>0.82199999999999995</v>
       </c>
       <c r="D7">
-        <v>0.96299999999999997</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="E7">
         <v>0.995</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7.4999999999999997E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="B9">
-        <v>5.5E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="C9">
         <v>7.0000000000000001E-3</v>
@@ -666,10 +666,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.157</v>
+        <v>0.152</v>
       </c>
       <c r="F9">
-        <v>0.69799999999999995</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="G9">
         <v>0.88300000000000001</v>
@@ -681,7 +681,7 @@
         <v>0.98</v>
       </c>
       <c r="J9">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
     </row>
   </sheetData>
